--- a/Excel/ActionTable.xlsx
+++ b/Excel/ActionTable.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -35,6 +35,24 @@
     <t xml:space="preserve">bCombo_Blend_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Combo_ResourceID_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bCombo_Blend_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combo_ResourceID_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bCombo_Blend_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combo_ResourceID_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bCombo_Blend_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Desc</t>
   </si>
   <si>
@@ -42,6 +60,9 @@
   </si>
   <si>
     <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALSE</t>
   </si>
   <si>
     <t xml:space="preserve">플레이어 기본 평타</t>
@@ -370,16 +391,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="36.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="8.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="8.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="5" style="1" width="17.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="8.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="8.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -398,162 +419,288 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="3"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="3"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -561,11 +708,11 @@
       <formula1>Enums!$A$1:$A$100</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C1:D1 C2:C17" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C1:J1 C2:C17 E2:E17 G2:G17 I2:I17" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D17" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D17 F2:F17 H2:H17 J2:J17" type="list">
       <formula1>"TRUE,FALSE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -594,7 +741,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -603,7 +750,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
